--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\vscode2\discord 2\dtmbot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F981F001-E4D3-403C-A3E1-079775766B08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4EB6996-B936-4A6D-A29C-86F6914171D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10080" yWindow="2265" windowWidth="18720" windowHeight="12180" xr2:uid="{BA55AFBA-6D23-4329-8FB0-7B85E1AD66B1}"/>
+    <workbookView xWindow="810" yWindow="1365" windowWidth="13860" windowHeight="12180" xr2:uid="{BA55AFBA-6D23-4329-8FB0-7B85E1AD66B1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Thời gian</t>
   </si>
@@ -48,9 +48,6 @@
   </si>
   <si>
     <t>ANNOUNCE_CHANNEL_ID</t>
-  </si>
-  <si>
-    <t>📢 Chúc các vị đạo hũ ngủ ngon!!</t>
   </si>
   <si>
     <t>📢  Chào buổi sáng các vị đạo hữu, chúc chư vị một ngày mới làm việc hiệu quả!!</t>
@@ -432,7 +429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D40FB27-6CC5-4AE8-8F40-483B1A15815F}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.7109375" style="2" customWidth="1"/>
@@ -459,17 +456,6 @@
         <v>3</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
-        <v>0.99583333333333335</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
     </row>
